--- a/astro-site/public/dl/pizza-shop-checklist-templates/BONUS-01-pizza-shop-pre-shift-meeting-template.xlsx
+++ b/astro-site/public/dl/pizza-shop-checklist-templates/BONUS-01-pizza-shop-pre-shift-meeting-template.xlsx
@@ -745,7 +745,7 @@
     <row r="6">
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Expected covers:</t>
+          <t>Expected covers + delivery / carryout orders:</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr"/>
@@ -885,7 +885,7 @@
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Bar staff:</t>
+          <t>Drivers on shift (and bar staff, if any):</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr"/>
